--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
   <si>
     <t>Filename</t>
   </si>
@@ -808,691 +808,703 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9945,0.0012,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0265,0.0000,0.0001,0.9946</t>
+    <t>0.9948,0.0011,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9859,0.0003,0.0001,0.0094</t>
+  </si>
+  <si>
+    <t>0.1184,0.0000,0.0000,0.9743</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9910,0.0087,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0018,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.5434,0.0085,0.4113,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0004,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.5212,0.0009,0.5728,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0002,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0002,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.1287,0.8783,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9388,0.0002,0.0629,0.0003</t>
+  </si>
+  <si>
+    <t>0.8702,0.0005,0.1561,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0019,0.9936,0.0004</t>
+  </si>
+  <si>
+    <t>0.0578,0.0001,0.9620,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0869,0.9157,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9863,0.0068,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0036</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8406,0.1871,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.0469,0.0005,0.9586,0.0009</t>
+  </si>
+  <si>
+    <t>0.0168,0.9794,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.0067,0.9854,0.0051,0.0020</t>
+  </si>
+  <si>
+    <t>0.0256,0.3054,0.4573,0.0088</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9984,0.0011</t>
+  </si>
+  <si>
+    <t>0.0043,0.0011,0.9906,0.0005</t>
+  </si>
+  <si>
+    <t>0.0076,0.0000,0.9930,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.0126,0.9914,0.0005</t>
+  </si>
+  <si>
+    <t>0.0051,0.9885,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9860,0.0006,0.6404</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0021,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0916,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0435,0.0005,0.9664,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0064,0.0004,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9989,0.0004</t>
+  </si>
+  <si>
+    <t>0.9952,0.0030,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0030,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0003,0.0002</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9989,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0022,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9950,0.0019,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9770,0.0029,0.0113,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0009,0.9962,0.0004</t>
-  </si>
-  <si>
-    <t>0.7179,0.0005,0.4105,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0651,0.9451,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0001,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9155,0.0009,0.0790,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0003,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9994,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0006</t>
-  </si>
-  <si>
-    <t>0.3101,0.6647,0.0049,0.0005</t>
-  </si>
-  <si>
-    <t>0.9887,0.0062,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9994,0.0064</t>
-  </si>
-  <si>
-    <t>0.0007,0.9974,0.0035,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0034,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9336,0.0021,0.0602,0.0004</t>
-  </si>
-  <si>
-    <t>0.0057,0.9923,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0149,0.9835,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0134,0.6757,0.1982,0.0088</t>
-  </si>
-  <si>
-    <t>0.0141,0.0216,0.9358,0.0029</t>
-  </si>
-  <si>
-    <t>0.0010,0.0025,0.9963,0.0004</t>
-  </si>
-  <si>
-    <t>0.0025,0.0001,0.9958,0.0014</t>
-  </si>
-  <si>
-    <t>0.0005,0.0031,0.9976,0.0003</t>
-  </si>
-  <si>
-    <t>0.0034,0.9930,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9895,0.0007,0.5613</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.4719,0.9944,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.9985,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0006,0.9968,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0003,0.9966,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9919,0.0046,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.0016,0.0083,0.9982,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9956,0.8779,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9991,0.0000</t>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9829,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0004,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0044,0.9986,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.9984,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.1547,0.0009,0.9048,0.0000</t>
+  </si>
+  <si>
+    <t>0.9645,0.0068,0.0240,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9925,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.7901,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.3006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.7784,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0323,0.9966</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0011,0.9996</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9264,0.9856,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.1157,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9512,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.1463,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9955,0.0061,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0021,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0163,0.9895,0.0004</t>
+  </si>
+  <si>
+    <t>0.9955,0.0001,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9989,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.9941,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.9957,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2688,0.7844,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.2244,0.0154,0.7059,0.0013</t>
+  </si>
+  <si>
+    <t>0.9691,0.0003,0.0334,0.0000</t>
+  </si>
+  <si>
+    <t>0.4531,0.2052,0.0732,0.0024</t>
+  </si>
+  <si>
+    <t>0.5057,0.0028,0.4661,0.0020</t>
+  </si>
+  <si>
+    <t>0.0001,0.2883,0.0003,0.9928</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0518,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9340,0.0520,0.0092,0.0003</t>
+  </si>
+  <si>
+    <t>0.9588,0.0351,0.0034,0.0007</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0012,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9972,0.0002,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.8977,0.9899,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.1213,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4441,0.0020,0.6277,0.0004</t>
+  </si>
+  <si>
+    <t>0.0078,0.0001,0.9931,0.0001</t>
+  </si>
+  <si>
+    <t>0.9677,0.0023,0.0124,0.0014</t>
+  </si>
+  <si>
+    <t>0.1815,0.0000,0.0000,0.9562</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9959,0.8488,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.9950,0.0008,0.0025</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0121,0.9838,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.1729,0.0000,0.0014,0.9162</t>
+  </si>
+  <si>
+    <t>0.9956,0.0014,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.1551,0.0149,0.8513,0.0021</t>
+  </si>
+  <si>
+    <t>0.9921,0.0002,0.0011,0.0038</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.6747,0.3491,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0875,0.8523,0.0179,0.0005</t>
+  </si>
+  <si>
+    <t>0.9205,0.0192,0.0280,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0011,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0461,0.9423,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.8987,0.0880,0.0059,0.0002</t>
+  </si>
+  <si>
+    <t>0.5944,0.4223,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.9916,0.0047,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.9978,0.0028,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9709,0.0449,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0016,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0011,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.9992,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0926,0.0026,0.9358,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0058,0.9912,0.0007</t>
+  </si>
+  <si>
+    <t>0.0026,0.0003,0.9965,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.0321,0.9522,0.0007</t>
+  </si>
+  <si>
+    <t>0.3684,0.0262,0.4052,0.0005</t>
+  </si>
+  <si>
+    <t>0.2191,0.0811,0.3897,0.0005</t>
+  </si>
+  <si>
+    <t>0.1217,0.0046,0.8672,0.0002</t>
+  </si>
+  <si>
+    <t>0.9515,0.0015,0.0282,0.0020</t>
+  </si>
+  <si>
+    <t>0.9689,0.0028,0.0136,0.0008</t>
+  </si>
+  <si>
+    <t>0.0230,0.9769,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.9975,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.2074,0.8517,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0178,0.9864,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.3473,0.7227,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9884,0.0100,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0000,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9758,0.0026,0.0061,0.0037</t>
+  </si>
+  <si>
+    <t>0.9590,0.0009,0.0337,0.0003</t>
+  </si>
+  <si>
+    <t>0.9145,0.0011,0.0767,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9986,0.0008</t>
+  </si>
+  <si>
+    <t>0.0090,0.0069,0.9760,0.0017</t>
+  </si>
+  <si>
+    <t>0.0011,0.9706,0.4767,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.0001,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0136,0.9917,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0020,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9962,0.0018,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0015,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0129,0.9969,0.0020</t>
+  </si>
+  <si>
+    <t>0.0105,0.1667,0.9107,0.0016</t>
+  </si>
+  <si>
+    <t>0.9961,0.0001,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0038,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1615,0.9963,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0084,0.0020,0.9836,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.0009,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0070,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9511,0.0000,0.0719,0.0000</t>
+  </si>
+  <si>
+    <t>0.8698,0.0001,0.1839,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0022,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9953,0.0037,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0016,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0007,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0074,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0089,0.9832,0.0008</t>
+  </si>
+  <si>
+    <t>0.0097,0.0033,0.9824,0.0005</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0460,0.0049,0.9589,0.0003</t>
-  </si>
-  <si>
-    <t>0.9693,0.0178,0.0059,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9943,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9689,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.1018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9078,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0007,0.9990</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.0022,0.9991</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0004,0.9998</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0217,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9690,0.9925,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9872,0.9463,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.7071,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.6181,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0020,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0019,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9935,0.0090,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0031,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0066,0.9935,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0001,0.9969,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9977,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.2619,0.8078,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0923,0.0075,0.8729,0.0022</t>
-  </si>
-  <si>
-    <t>0.9291,0.0010,0.0735,0.0002</t>
-  </si>
-  <si>
-    <t>0.0969,0.0372,0.7072,0.0051</t>
-  </si>
-  <si>
-    <t>0.9087,0.0033,0.0652,0.0009</t>
-  </si>
-  <si>
-    <t>0.0007,0.0235,0.0027,0.9910</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0351,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9985,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9212,0.0683,0.0069,0.0002</t>
-  </si>
-  <si>
-    <t>0.6717,0.2785,0.0127,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0007,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9958,0.0008,0.0003,0.0019</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.7578,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8600,0.9711,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0028,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0027,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9493,0.0084,0.0241,0.0014</t>
-  </si>
-  <si>
-    <t>0.0717,0.0001,0.9507,0.0001</t>
-  </si>
-  <si>
-    <t>0.9946,0.0005,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.4989,0.0000,0.0000,0.8379</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.8733,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.9930,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.5444,0.4776,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0261,0.0001,0.0021,0.9877</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.3650,0.0044,0.5734,0.0086</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9906,0.0008,0.0034,0.0023</t>
-  </si>
-  <si>
-    <t>0.5910,0.4070,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9795,0.0120,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.9850,0.0056,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.0488,0.9328,0.0061,0.0006</t>
-  </si>
-  <si>
-    <t>0.8013,0.1358,0.0090,0.0026</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9909,0.0065,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0433,0.9600,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.1489,0.8397,0.0059,0.0002</t>
-  </si>
-  <si>
-    <t>0.8097,0.2051,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.9771,0.0204,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.9949,0.0049,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0017,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.3054,0.8006,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9877,0.0051,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0078,0.9990,0.0015</t>
-  </si>
-  <si>
-    <t>0.0020,0.0004,0.9968,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0007,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0033,0.9936,0.0003</t>
-  </si>
-  <si>
-    <t>0.0281,0.0003,0.9805,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.0054,0.9806,0.0035</t>
-  </si>
-  <si>
-    <t>0.3042,0.0059,0.6665,0.0002</t>
-  </si>
-  <si>
-    <t>0.0293,0.1208,0.6316,0.0028</t>
-  </si>
-  <si>
-    <t>0.8716,0.0016,0.1282,0.0001</t>
-  </si>
-  <si>
-    <t>0.9874,0.0002,0.0091,0.0001</t>
-  </si>
-  <si>
-    <t>0.0146,0.0012,0.9801,0.0006</t>
-  </si>
-  <si>
-    <t>0.0096,0.9922,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9976,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0450,0.9616,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0161,0.9865,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.9963,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9746,0.0153,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0000,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9585,0.0009,0.0253,0.0018</t>
-  </si>
-  <si>
-    <t>0.9920,0.0002,0.0049,0.0000</t>
-  </si>
-  <si>
-    <t>0.9387,0.0050,0.0377,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9989,0.0020</t>
-  </si>
-  <si>
-    <t>0.0177,0.0105,0.9564,0.0036</t>
-  </si>
-  <si>
-    <t>0.0015,0.7836,0.8355,0.0003</t>
-  </si>
-  <si>
-    <t>0.0130,0.0001,0.9896,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0193,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9931,0.0057,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0021,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0129,0.9967,0.0032</t>
-  </si>
-  <si>
-    <t>0.0033,0.9284,0.0865,0.0035</t>
-  </si>
-  <si>
-    <t>0.9901,0.0003,0.0059,0.0005</t>
-  </si>
-  <si>
-    <t>0.0057,0.0001,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.1771,0.9892,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0423,0.0035,0.9463,0.0004</t>
-  </si>
-  <si>
-    <t>0.0042,0.0000,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0010,0.9941,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.1498,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.9949,0.0001,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.9250,0.0006,0.0834,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0015,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0028,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0186,0.0018,0.9715,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0038,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0047,0.2965,0.6393,0.0018</t>
-  </si>
-  <si>
-    <t>0.0163,0.0034,0.9724,0.0008</t>
-  </si>
-  <si>
-    <t>0.0041,0.0029,0.9925,0.0012</t>
-  </si>
-  <si>
-    <t>0.0235,0.0031,0.9623,0.0017</t>
-  </si>
-  <si>
-    <t>0.1220,0.0011,0.8597,0.0016</t>
-  </si>
-  <si>
-    <t>0.9455,0.0000,0.0020,0.0268</t>
-  </si>
-  <si>
-    <t>0.0004,0.0144,0.0001,0.9991</t>
-  </si>
-  <si>
-    <t>0.0397,0.0003,0.0042,0.9831</t>
-  </si>
-  <si>
-    <t>0.9170,0.0236,0.0047,0.0111</t>
+    <t>0.0078,0.0006,0.9876,0.0010</t>
+  </si>
+  <si>
+    <t>0.0173,0.0082,0.9635,0.0015</t>
+  </si>
+  <si>
+    <t>0.0173,0.0018,0.9703,0.0037</t>
+  </si>
+  <si>
+    <t>0.9677,0.0000,0.0020,0.0136</t>
+  </si>
+  <si>
+    <t>0.0010,0.0075,0.0002,0.9984</t>
+  </si>
+  <si>
+    <t>0.1037,0.0000,0.0001,0.9800</t>
+  </si>
+  <si>
+    <t>0.8867,0.0214,0.0076,0.0264</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1890,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1892,7 +1904,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1906,7 +1918,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1920,7 +1932,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1934,7 +1946,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1948,7 +1960,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1962,7 +1974,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1976,7 +1988,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1990,7 +2002,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2004,7 +2016,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2018,7 +2030,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2032,7 +2044,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2046,7 +2058,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2060,7 +2072,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2071,10 +2083,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2088,7 +2100,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2102,7 +2114,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2116,7 +2128,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2130,7 +2142,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2144,7 +2156,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2158,7 +2170,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2172,7 +2184,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2186,7 +2198,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2200,7 +2212,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2214,7 +2226,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2228,7 +2240,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2242,7 +2254,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2256,7 +2268,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2270,7 +2282,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2284,7 +2296,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2298,7 +2310,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2312,7 +2324,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2326,7 +2338,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2340,7 +2352,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,10 +2363,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2368,7 +2380,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2382,7 +2394,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,10 +2405,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2410,7 +2422,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2424,7 +2436,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2438,7 +2450,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2452,7 +2464,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2466,7 +2478,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2480,7 +2492,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2491,10 +2503,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2508,7 +2520,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2522,7 +2534,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2536,7 +2548,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2550,7 +2562,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2564,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2578,7 +2590,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2592,7 +2604,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2606,7 +2618,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2620,7 +2632,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2634,7 +2646,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2648,7 +2660,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2662,7 +2674,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2676,7 +2688,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2690,7 +2702,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2704,7 +2716,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2718,7 +2730,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2732,7 +2744,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2746,7 +2758,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2760,7 +2772,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2774,7 +2786,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2788,7 +2800,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2802,7 +2814,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2816,7 +2828,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2830,7 +2842,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2844,7 +2856,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2858,7 +2870,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2872,7 +2884,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2886,7 +2898,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2900,7 +2912,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2914,7 +2926,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2928,7 +2940,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2942,7 +2954,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2956,7 +2968,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2970,7 +2982,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2984,7 +2996,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2998,7 +3010,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3012,7 +3024,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3026,7 +3038,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3040,7 +3052,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3051,10 +3063,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,7 +3080,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,10 +3091,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3096,7 +3108,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3138,7 +3150,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3152,7 +3164,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3166,7 +3178,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3208,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3236,7 +3248,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3250,7 +3262,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3264,7 +3276,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3278,7 +3290,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3292,7 +3304,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3306,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3320,7 +3332,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3334,7 +3346,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3348,7 +3360,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3362,7 +3374,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3376,7 +3388,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3390,7 +3402,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3404,7 +3416,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3418,7 +3430,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3432,7 +3444,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>285</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3446,7 +3458,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3499,7 +3511,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
         <v>369</v>
@@ -3544,7 +3556,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3558,7 +3570,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3572,7 +3584,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3586,7 +3598,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3600,7 +3612,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3614,7 +3626,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3628,7 +3640,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3642,7 +3654,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3656,7 +3668,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3670,7 +3682,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3684,7 +3696,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3698,7 +3710,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3765,7 +3777,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>385</v>
@@ -3821,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>389</v>
@@ -3880,7 +3892,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>339</v>
+        <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3894,7 +3906,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3908,7 +3920,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3922,7 +3934,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3936,7 +3948,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3950,7 +3962,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3964,7 +3976,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3975,10 +3987,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3992,7 +4004,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4006,7 +4018,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4020,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4034,7 +4046,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4048,7 +4060,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4062,7 +4074,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4076,7 +4088,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4090,7 +4102,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4160,7 +4172,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4174,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4188,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4202,7 +4214,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4216,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>352</v>
+        <v>415</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4230,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4244,7 +4256,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4283,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
         <v>419</v>
@@ -4367,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
         <v>425</v>
@@ -4468,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>432</v>
+        <v>358</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4482,7 +4494,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>359</v>
+        <v>432</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4549,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
         <v>437</v>
@@ -4563,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D194" t="s">
         <v>438</v>
@@ -4577,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>439</v>
@@ -4605,7 +4617,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
         <v>441</v>
@@ -4787,7 +4799,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D210" t="s">
         <v>454</v>
@@ -4930,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>272</v>
+        <v>464</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4944,7 +4956,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4955,10 +4967,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4972,7 +4984,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4986,7 +4998,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5000,7 +5012,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5014,7 +5026,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5028,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5042,7 +5054,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5056,7 +5068,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5070,7 +5082,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5084,7 +5096,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5098,7 +5110,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5112,7 +5124,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5126,7 +5138,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5140,7 +5152,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>272</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5154,7 +5166,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5168,7 +5180,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>272</v>
+        <v>481</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5182,7 +5194,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5196,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5210,7 +5222,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5224,7 +5236,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5238,7 +5250,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5252,7 +5264,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5266,7 +5278,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5280,7 +5292,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5294,7 +5306,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5308,7 +5320,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>307</v>
+        <v>489</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5322,7 +5334,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5336,7 +5348,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5350,7 +5362,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5364,7 +5376,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5378,7 +5390,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5392,7 +5404,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5406,7 +5418,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>340</v>
+        <v>268</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5420,7 +5432,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>393</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5434,7 +5446,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
